--- a/output/pdf_financials_xlsx/WUC.xlsx
+++ b/output/pdf_financials_xlsx/WUC.xlsx
@@ -2071,13 +2071,13 @@
         </is>
       </c>
       <c r="B103" s="3" t="n">
-        <v>0</v>
+        <v>-0.027376</v>
       </c>
       <c r="C103" s="3" t="n">
-        <v>0</v>
+        <v>0.083575</v>
       </c>
       <c r="D103" s="3" t="n">
-        <v>0</v>
+        <v>-0.020966</v>
       </c>
     </row>
     <row r="104">
@@ -2119,13 +2119,13 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.165648</v>
+        <v>0.138272</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>-0.08908199999999999</v>
+        <v>-0.005507</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.015385</v>
+        <v>-0.005581</v>
       </c>
     </row>
     <row r="107">
@@ -3639,7 +3639,11 @@
           <t>Prepaid expenses and other current assets</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E34" s="5" t="n">
         <v>-0.027376</v>
       </c>
